--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -271,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -455,11 +455,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -608,6 +641,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -528,22 +528,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_casadelpensionista</t>
+          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO BDPR11G2 GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_casadelpensionista</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Oracle, SQL Server</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DGP.SOP | GG.UGD | TRANSVERSAL</t>
+          <t>Dirección de Gestión Previsional | Subdirección de Orientación Previsional | Unidad de Comunicaciones y Relacionamiento | Unidad de Gestión Documental</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2</t>
+          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO BDPR11G2 GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dispersión máx 0 BD por entidad · 25 BD sin catálogo de entidades</t>
+          <t>Dispersión máx 1 BD por entidad · 25 BD sin catálogo de entidades</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -596,12 +596,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
+          <t>BDPR11G4 BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -611,18 +611,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DGP | DGP.SOP</t>
+          <t>Dirección de Gestión Previsional | Secretaría Técnica del TAP | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Gestión de Derechos Previsionales | Subdirección de Orientación Previsional | Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
+          <t>BDPR11G4 BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dispersión máx 7 BD por entidad · 3 BD sin catálogo de entidades</t>
+          <t>Dispersión máx 8 BD por entidad · 3 BD sin catálogo de entidades</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DGP.SAG</t>
+          <t>Subdirección de Afiliación y Gestión de Aportes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DIP | DIP.SII</t>
+          <t>Dirección de Inversiones Previsionales | Subdirección de Inversiones Inmobiliarias</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DGP | DGP.SPP | DPG,PP y DPG.SAG | TRANSVERSAL, varias areas lo usan</t>
+          <t>Dirección de Gestión Previsional | Secretaría Técnica del TAP | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Gestión de Derechos Previsionales | Subdirección de Orientación Previsional | Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DGP | DGP.SAG | DGP.SGD | DGP.SOP | DPD.SFE | DRP | DRP.SFP | DRP.SPC | OAJ.AP | OTI.UIT | PE.DA | TRANSVERSAL, varias areas lo usan | pendiente de envio</t>
+          <t>Dirección de Gestión Previsional | Dirección de Regulación Previsional | Ejecutivo/a de Asuntos Procesales | Secretaría Técnica del TAP | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Finanzas y Estudios Previsionales | Subdirección de Fiscalización Previsional | Subdirección de Gestión de Derechos Previsionales | Subdirección de Orientación Previsional | Subdirección de Pago de Prestaciones | Subdirección de Programación y Control Previsional | Unidad Funcional de Defensoría del Asegurado | Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DGP | DGP.SAG | DGP.SOP</t>
+          <t>Secretaría Técnica del TAP | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Gestión de Derechos Previsionales | Subdirección de Orientación Previsional | Subdirección de Pago de Prestaciones</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SIGA_1782 SIGA_55 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
+          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G2 BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SIGA_1782 SIGA_55 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OAD | ORH | ORH.UGE | TRANSVERSAL</t>
+          <t>Dirección de Gestión Previsional | Oficina de Administración | Oficina de Recursos Humanos | Unidad de Gestión del Empleo y Compensaciones</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2</t>
+          <t>AppFabric_CachingServiceConfiguration BDPR11G2 BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dispersión máx 2 BD por entidad · 47 BD sin catálogo de entidades</t>
+          <t>Dispersión máx 3 BD por entidad · 47 BD sin catálogo de entidades</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DGP | DGP.SAG | DGP.SGD | GG.UGD</t>
+          <t>Dirección de Gestión Previsional | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Gestión de Derechos Previsionales | Unidad de Gestión Documental</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DGP.SOP | OTI | OTI.UIS | OTI.UIT | pendiente de envio</t>
+          <t>Dirección de Gestión Previsional | Oficina de Planeamiento, Presupuesto y Modernización | Oficina de Tecnologías de la Información | Subdirección de Afiliación y Gestión de Aportes | Subdirección de Orientación Previsional | Subdirección de Pago de Prestaciones | Unidad de Infraestructura y Soporte Tecnológico | Unidad de Ingeniería de Software</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>GG.UIG | ORH.UGE</t>
+          <t>Unidad de Gestión del Empleo y Compensaciones | Unidad de Integridad Institucional y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DPD.SFE | OTI.UIT</t>
+          <t>Subdirección de Finanzas y Estudios Previsionales | Unidad de Infraestructura y Soporte Tecnológico</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>OAJ.AP</t>
+          <t>Ejecutivo/a de Asuntos Procesales</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Vacíos / dispersión</t>
+          <t>Vacíos / solapamientos / dispersión</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -558,10 +558,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dispersión máx 1 BD por entidad · 25 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>26 fuente(s) de datos asociada(s); 25 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio. *</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,10 +626,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dispersión máx 8 BD por entidad · 3 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>11 fuente(s) de datos asociada(s); 3 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 8 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 8 de 8 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,10 +694,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dispersión máx 1 BD por entidad · 0 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio. *</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Asegurado/Afiliado, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -750,10 +762,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dispersión máx 3 BD por entidad · 0 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>3 fuente(s) de datos asociada(s); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -814,10 +830,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dispersión máx 9 BD por entidad · 1 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>10 fuente(s) de datos asociada(s); 1 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -882,10 +902,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dispersión máx 21 BD por entidad · 60 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>82 fuente(s) de datos asociada(s); 60 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 21 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 21 de 22 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -950,10 +974,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dispersión máx 7 BD por entidad · 2 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>9 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 7 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 7 de 7 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1018,10 +1046,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dispersión máx 3 BD por entidad · 47 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>50 fuente(s) de datos asociada(s); 47 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Documento, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Documento, Persona, Expediente/Trámite. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1086,10 +1118,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dispersión máx 9 BD por entidad · 8 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>17 fuente(s) de datos asociada(s); 8 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Notificación compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Notificación, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1154,10 +1190,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Dispersión máx 16 BD por entidad · 56 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>73 fuente(s) de datos asociada(s); 56 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 16 fuentes del dominio. Solapamiento: Documento, Aporte, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 16 de 17 fuentes con catálogo). Entidades relevantes: Documento, Aporte, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1198,10 +1238,14 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dispersión máx 0 BD por entidad · 0 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>Sin fuentes de datos asociadas al dominio (vacío total). *</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Sin entidades detectadas (fuentes sin catálogo físico o dominio no misional). *</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1266,10 +1310,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dispersión máx 2 BD por entidad · 2 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>4 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 2 fuentes del dominio. Solapamiento: Documento, Persona, Solicitud compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 2 de 2 fuentes con catálogo). Entidades relevantes: Documento, Persona, Solicitud, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1330,10 +1378,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dispersión máx 1 BD por entidad · 5 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>6 fuente(s) de datos asociada(s); 5 sin catálogo de entidades (cobertura del modelo parcial); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio. *</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Asegurado/Afiliado, Documento, Planilla. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1394,10 +1446,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dispersión máx 1 BD por entidad · 0 BD sin catálogo de entidades</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio. *</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Expediente/Trámite, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -558,12 +558,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>26 fuente(s) de datos asociada(s); 25 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio. *</t>
+          <t>26 fuente(s) de datos asociada(s); 25 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11 fuente(s) de datos asociada(s); 3 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 8 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>11 fuente(s) de datos asociada(s); 3 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 8 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 8 de 8 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 8 de 8 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio. *</t>
+          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Asegurado/Afiliado, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Asegurado/Afiliado, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3 fuente(s) de datos asociada(s); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>3 fuente(s) de datos asociada(s); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10 fuente(s) de datos asociada(s); 1 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>10 fuente(s) de datos asociada(s); 1 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>82 fuente(s) de datos asociada(s); 60 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 21 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>82 fuente(s) de datos asociada(s); 60 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 21 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 21 de 22 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 21 de 22 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 7 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>9 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 7 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 7 de 7 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 7 de 7 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50 fuente(s) de datos asociada(s); 47 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Documento, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>50 fuente(s) de datos asociada(s); 47 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Documento, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Documento, Persona, Expediente/Trámite. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Documento, Persona, Expediente/Trámite. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>17 fuente(s) de datos asociada(s); 8 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Notificación compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>17 fuente(s) de datos asociada(s); 8 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Notificación compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Notificación, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Notificación, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>73 fuente(s) de datos asociada(s); 56 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 16 fuentes del dominio. Solapamiento: Documento, Aporte, Persona compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>73 fuente(s) de datos asociada(s); 56 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 16 fuentes del dominio. Solapamiento: Documento, Aporte, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 16 de 17 fuentes con catálogo). Entidades relevantes: Documento, Aporte, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 16 de 17 fuentes con catálogo). Entidades relevantes: Documento, Aporte, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sin fuentes de datos asociadas al dominio (vacío total). *</t>
+          <t>Sin fuentes de datos asociadas al dominio (vacío total).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Sin entidades detectadas (fuentes sin catálogo físico o dominio no misional). *</t>
+          <t>Sin entidades detectadas (fuentes sin catálogo físico o dominio no misional).</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 2 fuentes del dominio. Solapamiento: Documento, Persona, Solicitud compartida(s) por ≥2 fuentes (posible duplicidad). *</t>
+          <t>4 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 2 fuentes del dominio. Solapamiento: Documento, Persona, Solicitud compartida(s) por ≥2 fuentes (posible duplicidad).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 2 de 2 fuentes con catálogo). Entidades relevantes: Documento, Persona, Solicitud, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 2 de 2 fuentes con catálogo). Entidades relevantes: Documento, Persona, Solicitud, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 fuente(s) de datos asociada(s); 5 sin catálogo de entidades (cobertura del modelo parcial); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio. *</t>
+          <t>6 fuente(s) de datos asociada(s); 5 sin catálogo de entidades (cobertura del modelo parcial); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Asegurado/Afiliado, Documento, Planilla. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Asegurado/Afiliado, Documento, Planilla. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio. *</t>
+          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Expediente/Trámite, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC). *</t>
+          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Expediente/Trámite, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
         </is>
       </c>
     </row>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -558,12 +558,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>26 fuente(s) de datos asociada(s); 25 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio.</t>
+          <t>De 26 fuentes del dominio, solo 1 con catálogo de entidades documentado (cobertura del modelo parcial). El 15% de las columnas tiene comentarios, por lo que la documentación del dato es limitada.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>La entidad predominante del dominio es 'Aporte'. Conviene ampliar el catálogo de las 25 fuentes sin documentar para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11 fuente(s) de datos asociada(s); 3 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 8 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 11 fuentes ('Documento' en 8 BD, 'Solicitud' en 8 BD, 'Aporte' en 8 BD, 'Persona' en 8 BD), sin un maestro único consolidado. Además, solo el 55% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 8 de 8 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 8 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Solicitud, Aporte para reducir la fragmentación. Debe mejorarse la documentación (55% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio.</t>
+          <t>El dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes. El 45% de las columnas tiene comentarios; conviene mejorar la documentación del dato.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Asegurado/Afiliado, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>La entidad predominante del dominio es 'Documento'. Conviene mejorar la documentación (45% columnas comentadas) para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3 fuente(s) de datos asociada(s); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 3 fuentes ('Aporte' en 3 BD, 'Persona' en 3 BD, 'Documento' en 3 BD, 'Asegurado/Afiliado' en 3 BD), sin un maestro único consolidado. Además, solo el 22% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Aporte' es la entidad más transversal del dominio (presente en 3 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Documento para reducir la fragmentación. Debe mejorarse la documentación (22% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10 fuente(s) de datos asociada(s); 1 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Solicitud, Aporte compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 10 fuentes ('Documento' en 9 BD, 'Solicitud' en 9 BD, 'Aporte' en 9 BD, 'Expediente/Trámite' en 9 BD), sin un maestro único consolidado. Además, solo el 40% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Solicitud, Aporte, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 9 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Solicitud, Aporte para reducir la fragmentación. Debe mejorarse la documentación (40% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>82 fuente(s) de datos asociada(s); 60 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 21 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 82 fuentes ('Documento' en 21 BD, 'Expediente/Trámite' en 21 BD, 'Persona' en 20 BD, 'Solicitud' en 20 BD), sin un maestro único consolidado. Además, solo el 34% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 21 de 22 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 21 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Expediente/Trámite, Persona para reducir la fragmentación. Debe mejorarse la documentación (34% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 7 fuentes del dominio. Solapamiento: Aporte, Persona, Documento compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 9 fuentes ('Aporte' en 7 BD, 'Persona' en 7 BD, 'Documento' en 7 BD, 'Asegurado/Afiliado' en 7 BD), sin un maestro único consolidado. Además, solo el 23% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 7 de 7 fuentes con catálogo). Entidades relevantes: Aporte, Persona, Documento, Asegurado/Afiliado. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Aporte' es la entidad más transversal del dominio (presente en 7 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Documento para reducir la fragmentación. Debe mejorarse la documentación (23% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50 fuente(s) de datos asociada(s); 47 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Aporte' aparece en 3 fuentes del dominio. Solapamiento: Aporte, Documento, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 50 fuentes ('Aporte' en 3 BD, 'Documento' en 3 BD, 'Persona' en 3 BD, 'Expediente/Trámite' en 3 BD), sin un maestro único consolidado. Además, solo el 57% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 3 de 3 fuentes con catálogo). Entidades relevantes: Aporte, Documento, Persona, Expediente/Trámite. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Aporte' es la entidad más transversal del dominio (presente en 3 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Documento, Persona para reducir la fragmentación. Debe mejorarse la documentación (57% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>17 fuente(s) de datos asociada(s); 8 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 9 fuentes del dominio. Solapamiento: Documento, Expediente/Trámite, Notificación compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 17 fuentes ('Documento' en 9 BD, 'Expediente/Trámite' en 9 BD, 'Notificación' en 9 BD, 'Persona' en 8 BD), sin un maestro único consolidado. Además, solo el 48% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 9 de 9 fuentes con catálogo). Entidades relevantes: Documento, Expediente/Trámite, Notificación, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 9 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Expediente/Trámite, Notificación para reducir la fragmentación. Debe mejorarse la documentación (48% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>73 fuente(s) de datos asociada(s); 56 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 16 fuentes del dominio. Solapamiento: Documento, Aporte, Persona compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 73 fuentes ('Documento' en 16 BD, 'Aporte' en 15 BD, 'Persona' en 15 BD, 'Solicitud' en 15 BD), sin un maestro único consolidado. Además, solo el 24% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 16 de 17 fuentes con catálogo). Entidades relevantes: Documento, Aporte, Persona, Solicitud. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 16 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Aporte, Persona para reducir la fragmentación. Debe mejorarse la documentación (24% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sin fuentes de datos asociadas al dominio (vacío total).</t>
+          <t>Sin fuentes de datos asociadas en el inventario: vacío total (no hay sistemas ni BD mapeadas).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Sin entidades detectadas (fuentes sin catálogo físico o dominio no misional).</t>
+          <t>Sin entidades detectadas (fuentes sin catálogo o dominio no misional); requiere identificar sus sistemas de soporte para el modelado.</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4 fuente(s) de datos asociada(s); 2 sin catálogo de entidades (cobertura del modelo parcial). Dispersión: la entidad 'Documento' aparece en 2 fuentes del dominio. Solapamiento: Documento, Persona, Solicitud compartida(s) por ≥2 fuentes (posible duplicidad).</t>
+          <t>Las entidades core del dominio están fragmentadas entre varias de sus 4 fuentes ('Documento' en 2 BD, 'Persona' en 2 BD, 'Solicitud' en 2 BD, 'Expediente/Trámite' en 2 BD), sin un maestro único consolidado. Además, solo el 46% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 2 de 2 fuentes con catálogo). Entidades relevantes: Documento, Persona, Solicitud, Expediente/Trámite. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>'Documento' es la entidad más transversal del dominio (presente en 2 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Solicitud para reducir la fragmentación. Debe mejorarse la documentación (46% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 fuente(s) de datos asociada(s); 5 sin catálogo de entidades (cobertura del modelo parcial); 1 proceso(s) del dominio sin sistema (vacío funcional). Dispersión: la entidad 'Aporte' aparece en 1 fuentes del dominio.</t>
+          <t>De 6 fuentes del dominio, solo 1 con catálogo de entidades documentado (cobertura del modelo parcial). El 81% de las columnas tiene comentarios, por lo que la documentación del dato es limitada.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Aporte' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Aporte, Asegurado/Afiliado, Documento, Planilla. 'Aporte' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>La entidad predominante del dominio es 'Aporte'. Conviene ampliar el catálogo de las 5 fuentes sin documentar para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 fuente(s) de datos asociada(s). Dispersión: la entidad 'Documento' aparece en 1 fuentes del dominio.</t>
+          <t>El dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes. El 66% de las columnas tiene comentarios; conviene mejorar la documentación del dato.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Aporta principalmente la entidad 'Documento' (presente en 1 de 1 fuentes con catálogo). Entidades relevantes: Documento, Recaudación/Pago, Expediente/Trámite, Persona. 'Documento' candidata a entidad maestra del modelo conceptual BDI. Alineación con el SIIP pendiente (dominios de datos aún no definidos en el MC).</t>
+          <t>La entidad predominante del dominio es 'Documento'. Conviene mejorar la documentación (66% columnas comentadas) para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
         </is>
       </c>
     </row>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -558,12 +558,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>De 26 fuentes del dominio, solo 1 con catálogo de entidades documentado (cobertura del modelo parcial). El 15% de las columnas tiene comentarios, por lo que la documentación del dato es limitada.</t>
+          <t>Severidad Crítica (15% documentado): de 26 fuentes del dominio, solo 1 tiene su estructura física catalogada (cobertura del modelo parcial); el 15% de las columnas tiene comentarios.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>La entidad predominante del dominio es 'Aporte'. Conviene ampliar el catálogo de las 25 fuentes sin documentar para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Aporte, Persona, Documento, Asegurado/Afiliado, Empleador/Aportante, Recaudación/Pago, Pensión/Pensionista, SCTR, Expediente/Trámite, Planilla, Solicitud, Beneficiario, Resolución, Derecho previsional, Prestación/Beneficio, Notificación, Fiscalización, Inversión/FCR.</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 11 fuentes ('Documento' en 8 BD, 'Solicitud' en 8 BD, 'Aporte' en 8 BD, 'Persona' en 8 BD), sin un maestro único consolidado. Además, solo el 55% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Baja (55% documentado): las entidades core están fragmentadas entre varias de sus 11 fuentes ('Documento' en 8 BD, 'Solicitud' en 8 BD, 'Aporte' en 8 BD, 'Persona' en 8 BD), sin un maestro único consolidado; el 55% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 8 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Solicitud, Aporte para reducir la fragmentación. Debe mejorarse la documentación (55% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Solicitud, Aporte, Persona, Expediente/Trámite, Beneficiario, Notificación, Recaudación/Pago, Pensión/Pensionista, Planilla, Prestación/Beneficio, Derecho previsional, Resolución, Asegurado/Afiliado, SCTR, Fiscalización, Empleador/Aportante, Inversión/FCR.</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>El dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes. El 45% de las columnas tiene comentarios; conviene mejorar la documentación del dato.</t>
+          <t>Severidad Media (45% documentado): el dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes; el 45% de las columnas tiene comentarios.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>La entidad predominante del dominio es 'Documento'. Conviene mejorar la documentación (45% columnas comentadas) para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Recaudación/Pago, Asegurado/Afiliado, Persona, Solicitud, Expediente/Trámite, Aporte, Empleador/Aportante, Beneficiario, Pensión/Pensionista, Planilla, Resolución, SCTR, Notificación, Derecho previsional, Prestación/Beneficio.</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 3 fuentes ('Aporte' en 3 BD, 'Persona' en 3 BD, 'Documento' en 3 BD, 'Asegurado/Afiliado' en 3 BD), sin un maestro único consolidado. Además, solo el 22% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Crítica (22% documentado): las entidades core están fragmentadas entre varias de sus 3 fuentes ('Aporte' en 3 BD, 'Persona' en 3 BD, 'Documento' en 3 BD, 'Asegurado/Afiliado' en 3 BD), sin un maestro único consolidado; el 22% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>'Aporte' es la entidad más transversal del dominio (presente en 3 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Documento para reducir la fragmentación. Debe mejorarse la documentación (22% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Aporte, Persona, Documento, Asegurado/Afiliado, Empleador/Aportante, Recaudación/Pago, Pensión/Pensionista, SCTR, Planilla, Inversión/FCR, Expediente/Trámite, Solicitud, Beneficiario, Prestación/Beneficio, Derecho previsional, Notificación, Resolución, Fiscalización.</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 10 fuentes ('Documento' en 9 BD, 'Solicitud' en 9 BD, 'Aporte' en 9 BD, 'Expediente/Trámite' en 9 BD), sin un maestro único consolidado. Además, solo el 40% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Media (40% documentado): las entidades core están fragmentadas entre varias de sus 10 fuentes ('Documento' en 9 BD, 'Solicitud' en 9 BD, 'Aporte' en 9 BD, 'Expediente/Trámite' en 9 BD), sin un maestro único consolidado; el 40% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 9 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Solicitud, Aporte para reducir la fragmentación. Debe mejorarse la documentación (40% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Solicitud, Aporte, Expediente/Trámite, Persona, Notificación, Recaudación/Pago, Pensión/Pensionista, Beneficiario, Asegurado/Afiliado, Planilla, Resolución, Derecho previsional, Prestación/Beneficio, SCTR, Fiscalización, Empleador/Aportante, Apelación, Inversión/FCR.</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 82 fuentes ('Documento' en 21 BD, 'Expediente/Trámite' en 21 BD, 'Persona' en 20 BD, 'Solicitud' en 20 BD), sin un maestro único consolidado. Además, solo el 34% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Alta (34% documentado): las entidades core están fragmentadas entre varias de sus 82 fuentes ('Documento' en 21 BD, 'Expediente/Trámite' en 21 BD, 'Persona' en 20 BD, 'Solicitud' en 20 BD), sin un maestro único consolidado; el 34% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 21 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Expediente/Trámite, Persona para reducir la fragmentación. Debe mejorarse la documentación (34% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Expediente/Trámite, Persona, Solicitud, Notificación, Aporte, Pensión/Pensionista, Recaudación/Pago, Empleador/Aportante, Asegurado/Afiliado, Beneficiario, Planilla, Resolución, SCTR, Prestación/Beneficio, Derecho previsional, Fiscalización, Inversión/FCR, Apelación.</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 9 fuentes ('Aporte' en 7 BD, 'Persona' en 7 BD, 'Documento' en 7 BD, 'Asegurado/Afiliado' en 7 BD), sin un maestro único consolidado. Además, solo el 23% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Alta (23% documentado): las entidades core están fragmentadas entre varias de sus 9 fuentes ('Aporte' en 7 BD, 'Persona' en 7 BD, 'Documento' en 7 BD, 'Asegurado/Afiliado' en 7 BD), sin un maestro único consolidado; el 23% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>'Aporte' es la entidad más transversal del dominio (presente en 7 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Documento para reducir la fragmentación. Debe mejorarse la documentación (23% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Aporte, Persona, Documento, Asegurado/Afiliado, Recaudación/Pago, Pensión/Pensionista, Beneficiario, Solicitud, Expediente/Trámite, SCTR, Planilla, Prestación/Beneficio, Derecho previsional, Resolución, Notificación, Fiscalización, Empleador/Aportante, Inversión/FCR.</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 50 fuentes ('Aporte' en 3 BD, 'Documento' en 3 BD, 'Persona' en 3 BD, 'Expediente/Trámite' en 3 BD), sin un maestro único consolidado. Además, solo el 57% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Mínima (57% documentado): las entidades core están fragmentadas entre varias de sus 50 fuentes ('Aporte' en 3 BD, 'Documento' en 3 BD, 'Persona' en 3 BD, 'Expediente/Trámite' en 3 BD), sin un maestro único consolidado; el 57% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>'Aporte' es la entidad más transversal del dominio (presente en 3 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Documento, Persona para reducir la fragmentación. Debe mejorarse la documentación (57% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Aporte, Documento, Persona, Expediente/Trámite, Solicitud, Notificación, Beneficiario, Asegurado/Afiliado, Empleador/Aportante, Planilla, Pensión/Pensionista, Recaudación/Pago, Inversión/FCR, SCTR, Resolución, Prestación/Beneficio, Derecho previsional, Fiscalización.</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 17 fuentes ('Documento' en 9 BD, 'Expediente/Trámite' en 9 BD, 'Notificación' en 9 BD, 'Persona' en 8 BD), sin un maestro único consolidado. Además, solo el 48% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Baja (48% documentado): las entidades core están fragmentadas entre varias de sus 17 fuentes ('Documento' en 9 BD, 'Expediente/Trámite' en 9 BD, 'Notificación' en 9 BD, 'Persona' en 8 BD), sin un maestro único consolidado; el 48% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 9 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Expediente/Trámite, Notificación para reducir la fragmentación. Debe mejorarse la documentación (48% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Expediente/Trámite, Notificación, Persona, Solicitud, Aporte, Asegurado/Afiliado, Pensión/Pensionista, Empleador/Aportante, Recaudación/Pago, Beneficiario, Planilla, SCTR, Resolución, Prestación/Beneficio, Fiscalización, Derecho previsional, Inversión/FCR.</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 73 fuentes ('Documento' en 16 BD, 'Aporte' en 15 BD, 'Persona' en 15 BD, 'Solicitud' en 15 BD), sin un maestro único consolidado. Además, solo el 24% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Alta (24% documentado): las entidades core están fragmentadas entre varias de sus 73 fuentes ('Documento' en 16 BD, 'Aporte' en 15 BD, 'Persona' en 15 BD, 'Solicitud' en 15 BD), sin un maestro único consolidado; el 24% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 16 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Aporte, Persona para reducir la fragmentación. Debe mejorarse la documentación (24% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Aporte, Persona, Solicitud, Expediente/Trámite, Notificación, Pensión/Pensionista, Recaudación/Pago, SCTR, Beneficiario, Asegurado/Afiliado, Empleador/Aportante, Planilla, Prestación/Beneficio, Resolución, Derecho previsional, Fiscalización, Inversión/FCR, Apelación.</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sin fuentes de datos asociadas en el inventario: vacío total (no hay sistemas ni BD mapeadas).</t>
+          <t>Severidad Crítica (0% documentado): sin fuentes de datos asociadas en el inventario (vacío total: no hay sistemas ni BD mapeadas).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Sin entidades detectadas (fuentes sin catálogo o dominio no misional); requiere identificar sus sistemas de soporte para el modelado.</t>
+          <t>No aporta entidades al modelo conceptual (sin estructura catalogada).</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Las entidades core del dominio están fragmentadas entre varias de sus 4 fuentes ('Documento' en 2 BD, 'Persona' en 2 BD, 'Solicitud' en 2 BD, 'Expediente/Trámite' en 2 BD), sin un maestro único consolidado. Además, solo el 46% de las columnas de esas fuentes tiene comentarios, lo que limita el entendimiento y la trazabilidad del dato.</t>
+          <t>Severidad Baja (46% documentado): las entidades core están fragmentadas entre varias de sus 4 fuentes ('Documento' en 2 BD, 'Persona' en 2 BD, 'Solicitud' en 2 BD, 'Expediente/Trámite' en 2 BD), sin un maestro único consolidado; el 46% de las columnas de esas fuentes está documentado con comentarios.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>'Documento' es la entidad más transversal del dominio (presente en 2 fuentes): candidata a entidad maestra única del BDI, a consolidar junto con Persona, Solicitud para reducir la fragmentación. Debe mejorarse la documentación (46% columnas comentadas) de cara al modelado. Correspondencia detallada con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Persona, Solicitud, Expediente/Trámite, Aporte, Empleador/Aportante, Pensión/Pensionista, Notificación, SCTR, Recaudación/Pago, Asegurado/Afiliado, Beneficiario, Planilla, Resolución, Derecho previsional, Prestación/Beneficio, Fiscalización.</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>De 6 fuentes del dominio, solo 1 con catálogo de entidades documentado (cobertura del modelo parcial). El 81% de las columnas tiene comentarios, por lo que la documentación del dato es limitada.</t>
+          <t>Severidad Mínima (81% documentado): de 6 fuentes del dominio, solo 1 tiene su estructura física catalogada (cobertura del modelo parcial); el 81% de las columnas tiene comentarios.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>La entidad predominante del dominio es 'Aporte'. Conviene ampliar el catálogo de las 5 fuentes sin documentar para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Aporte, Asegurado/Afiliado, Documento, Planilla, Persona, Empleador/Aportante, Inversión/FCR, Solicitud, Recaudación/Pago, SCTR, Pensión/Pensionista, Beneficiario, Derecho previsional, Prestación/Beneficio, Notificación, Expediente/Trámite.</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>El dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes. El 66% de las columnas tiene comentarios; conviene mejorar la documentación del dato.</t>
+          <t>Severidad Mínima (66% documentado): el dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes; el 66% de las columnas tiene comentarios.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>La entidad predominante del dominio es 'Documento'. Conviene mejorar la documentación (66% columnas comentadas) para el modelado. Correspondencia con el SIIP pendiente (dominios de datos no definidos en el MC).</t>
+          <t>Entidades que aporta al modelo conceptual: Documento, Recaudación/Pago, Expediente/Trámite, Persona, Notificación, Solicitud, Resolución, Pensión/Pensionista, Apelación, Aporte, Beneficiario, Empleador/Aportante.</t>
         </is>
       </c>
     </row>

--- a/client/public/artefactos/ADI-04.xlsx
+++ b/client/public/artefactos/ADI-04.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Severidad Crítica (15% documentado): de 26 fuentes del dominio, solo 1 tiene su estructura física catalogada (cobertura del modelo parcial); el 15% de las columnas tiene comentarios.</t>
+          <t>Dispersión no evaluable con la cobertura actual: solo 1 de 26 fuentes tiene estructura física catalogada. La documentación del dato es muy deficiente (15% de columnas comentadas), lo que impide entenderlo sin apoyo del gestor.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Severidad Baja (55% documentado): las entidades core están fragmentadas entre varias de sus 11 fuentes ('Documento' en 8 BD, 'Solicitud' en 8 BD, 'Aporte' en 8 BD, 'Persona' en 8 BD), sin un maestro único consolidado; el 55% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión muy alta: entidades como 'Documento', 'Solicitud', 'Aporte' están presentes en varias fuentes (hasta 8 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es aceptable (55% de columnas comentadas), aunque mejorable.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Severidad Media (45% documentado): el dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes; el 45% de las columnas tiene comentarios.</t>
+          <t>Dispersión baja (favorable): la información se concentra en 1 fuente, sin fragmentación entre fuentes. La documentación del dato es parcial (45% de columnas comentadas); conviene completarla.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Severidad Crítica (22% documentado): las entidades core están fragmentadas entre varias de sus 3 fuentes ('Aporte' en 3 BD, 'Persona' en 3 BD, 'Documento' en 3 BD, 'Asegurado/Afiliado' en 3 BD), sin un maestro único consolidado; el 22% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión moderada: entidades como 'Aporte', 'Persona', 'Documento' están presentes en varias fuentes (hasta 3 BD), evidenciando fragmentación sin un maestro consolidado, lo que invita a evaluar un maestro único. La documentación del dato es muy deficiente (22% de columnas comentadas), lo que impide entenderlo sin apoyo del gestor.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Severidad Media (40% documentado): las entidades core están fragmentadas entre varias de sus 10 fuentes ('Documento' en 9 BD, 'Solicitud' en 9 BD, 'Aporte' en 9 BD, 'Expediente/Trámite' en 9 BD), sin un maestro único consolidado; el 40% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión muy alta: entidades como 'Documento', 'Solicitud', 'Aporte' están presentes en varias fuentes (hasta 9 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es parcial (40% de columnas comentadas); conviene completarla.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Severidad Alta (34% documentado): las entidades core están fragmentadas entre varias de sus 82 fuentes ('Documento' en 21 BD, 'Expediente/Trámite' en 21 BD, 'Persona' en 20 BD, 'Solicitud' en 20 BD), sin un maestro único consolidado; el 34% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión muy alta: entidades como 'Documento', 'Expediente/Trámite', 'Persona' están presentes en varias fuentes (hasta 21 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es escasa (34% de columnas comentadas), lo que limita su entendimiento.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Severidad Alta (23% documentado): las entidades core están fragmentadas entre varias de sus 9 fuentes ('Aporte' en 7 BD, 'Persona' en 7 BD, 'Documento' en 7 BD, 'Asegurado/Afiliado' en 7 BD), sin un maestro único consolidado; el 23% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión alta: entidades como 'Aporte', 'Persona', 'Documento' están presentes en varias fuentes (hasta 7 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es escasa (23% de columnas comentadas), lo que limita su entendimiento.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Severidad Mínima (57% documentado): las entidades core están fragmentadas entre varias de sus 50 fuentes ('Aporte' en 3 BD, 'Documento' en 3 BD, 'Persona' en 3 BD, 'Expediente/Trámite' en 3 BD), sin un maestro único consolidado; el 57% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión moderada: entidades como 'Aporte', 'Documento', 'Persona' están presentes en varias fuentes (hasta 3 BD), evidenciando fragmentación sin un maestro consolidado, lo que invita a evaluar un maestro único. La documentación del dato es adecuada (57% de columnas comentadas).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Severidad Baja (48% documentado): las entidades core están fragmentadas entre varias de sus 17 fuentes ('Documento' en 9 BD, 'Expediente/Trámite' en 9 BD, 'Notificación' en 9 BD, 'Persona' en 8 BD), sin un maestro único consolidado; el 48% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión muy alta: entidades como 'Documento', 'Expediente/Trámite', 'Notificación' están presentes en varias fuentes (hasta 9 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es aceptable (48% de columnas comentadas), aunque mejorable.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Severidad Alta (24% documentado): las entidades core están fragmentadas entre varias de sus 73 fuentes ('Documento' en 16 BD, 'Aporte' en 15 BD, 'Persona' en 15 BD, 'Solicitud' en 15 BD), sin un maestro único consolidado; el 24% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión muy alta: entidades como 'Documento', 'Aporte', 'Persona' están presentes en varias fuentes (hasta 16 BD), evidenciando fragmentación sin un maestro consolidado — situación desfavorable que justifica consolidar un maestro único en el BDI. La documentación del dato es escasa (24% de columnas comentadas), lo que limita su entendimiento.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Severidad Crítica (0% documentado): sin fuentes de datos asociadas en el inventario (vacío total: no hay sistemas ni BD mapeadas).</t>
+          <t>Sin fuentes de datos asociadas en el inventario (vacío total: no hay sistemas ni BD mapeadas).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Severidad Baja (46% documentado): las entidades core están fragmentadas entre varias de sus 4 fuentes ('Documento' en 2 BD, 'Persona' en 2 BD, 'Solicitud' en 2 BD, 'Expediente/Trámite' en 2 BD), sin un maestro único consolidado; el 46% de las columnas de esas fuentes está documentado con comentarios.</t>
+          <t>Dispersión moderada: entidades como 'Documento', 'Persona', 'Solicitud' están presentes en varias fuentes (hasta 2 BD), evidenciando fragmentación sin un maestro consolidado, lo que invita a evaluar un maestro único. La documentación del dato es aceptable (46% de columnas comentadas), aunque mejorable.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Severidad Mínima (81% documentado): de 6 fuentes del dominio, solo 1 tiene su estructura física catalogada (cobertura del modelo parcial); el 81% de las columnas tiene comentarios.</t>
+          <t>Dispersión no evaluable con la cobertura actual: solo 1 de 6 fuentes tiene estructura física catalogada. La documentación del dato es adecuada (81% de columnas comentadas).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Severidad Mínima (66% documentado): el dominio se concentra en 1 fuente, sin fragmentación de entidades entre fuentes; el 66% de las columnas tiene comentarios.</t>
+          <t>Dispersión baja (favorable): la información se concentra en 1 fuente, sin fragmentación entre fuentes. La documentación del dato es adecuada (66% de columnas comentadas).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
